--- a/Dynamic Data Sources for Power Query/Dynamic Data Sources for Power Query (EN).xlsx
+++ b/Dynamic Data Sources for Power Query/Dynamic Data Sources for Power Query (EN).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sgoos\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{872D3F3D-8FA1-4ED6-9006-BCCF03DB04C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C94D47EB-ED4E-4A00-BCB8-9540F91388AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2E1A5ED9-1123-42E8-9B91-2AFAA7DA74F0}"/>
   </bookViews>
@@ -105,7 +105,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="55">
   <si>
     <t>Regio</t>
   </si>
@@ -224,9 +224,6 @@
     <t>File extention</t>
   </si>
   <si>
-    <t>With date?</t>
-  </si>
-  <si>
     <t>REGEX search pattern</t>
   </si>
   <si>
@@ -267,6 +264,12 @@
   </si>
   <si>
     <t>(CTRL +) ALT + F5 to Refresh</t>
+  </si>
+  <si>
+    <t>Include date?</t>
+  </si>
+  <si>
+    <t>27-09-2026</t>
   </si>
 </sst>
 </file>
@@ -463,7 +466,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -514,6 +517,9 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -522,64 +528,64 @@
   </cellStyles>
   <dxfs count="51">
     <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="19" formatCode="d/m/yyyy"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="19" formatCode="d/m/yyyy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -1105,11 +1111,11 @@
     <tableColumn id="1" xr3:uid="{374DF0B0-4CE0-4425-BDC7-4750CCCCC24D}" name="ID" dataDxfId="48"/>
     <tableColumn id="2" xr3:uid="{19BA6350-DC78-4E0F-B2A3-EF468F7B49D4}" name="Filepath" dataDxfId="47"/>
     <tableColumn id="3" xr3:uid="{7AEABA5A-E1A3-43D4-A3A2-DB2C34F759CE}" name="Subfolder" dataDxfId="46">
-      <calculatedColumnFormula array="1">IFERROR(IF(_xlfn.REGEXTEST(INDIRECT(cfg_sources[[#This Row],[Filepath]]), "://"), "src", ""),"")</calculatedColumnFormula>
+      <calculatedColumnFormula array="1">IFERROR(IF(_xlfn.REGEXTEST(INDIRECT(cfg_sources[[#This Row],[Filepath]]), "://"), "source_data", ""),"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{9E468012-BF1A-4971-94A6-6E64D1D9724A}" name="Filename (base)" dataDxfId="45"/>
     <tableColumn id="5" xr3:uid="{0B61A674-0407-454C-B7A8-068FA21194CD}" name="File extention" dataDxfId="44"/>
-    <tableColumn id="6" xr3:uid="{E5E2BE14-7C9B-47DA-8EA4-D711C6C34677}" name="With date?" dataDxfId="43"/>
+    <tableColumn id="6" xr3:uid="{E5E2BE14-7C9B-47DA-8EA4-D711C6C34677}" name="Include date?" dataDxfId="43"/>
     <tableColumn id="7" xr3:uid="{03635881-CF8B-46ED-91B2-0123B579183B}" name="Overwrite date with" dataDxfId="42"/>
     <tableColumn id="8" xr3:uid="{7F26D087-AC85-4D29-A914-A2EAB117BD6F}" name="REGEX search pattern" dataDxfId="41"/>
     <tableColumn id="9" xr3:uid="{85E1E00B-E9CC-44B4-9CE0-C427BC3BD4AF}" name="REGEX replace with" dataDxfId="40"/>
@@ -1150,14 +1156,14 @@
     <tableColumn id="6" xr3:uid="{E19BC787-F754-45BB-9B0D-E800317B8F5A}" uniqueName="6" name="Opdrachtgever" queryTableFieldId="6" dataDxfId="22"/>
     <tableColumn id="7" xr3:uid="{7E1313A5-9EF6-4A74-A8B7-4ADB98D7A0F9}" uniqueName="7" name="Prioriteit" queryTableFieldId="7" dataDxfId="21"/>
     <tableColumn id="8" xr3:uid="{11AB329E-2552-4F1E-AF7B-965CA738DC01}" uniqueName="8" name="Status" queryTableFieldId="8" dataDxfId="20"/>
-    <tableColumn id="9" xr3:uid="{57E6EFC5-3E51-4CA8-999D-907B33F7A7EA}" uniqueName="9" name="Startdatum" queryTableFieldId="9" dataDxfId="1"/>
-    <tableColumn id="10" xr3:uid="{AAB42422-E2C6-40F3-98D1-D47D061F6522}" uniqueName="10" name="Einddatum_gepland" queryTableFieldId="10" dataDxfId="0"/>
-    <tableColumn id="11" xr3:uid="{F7A8C4D0-5031-4E2A-9F30-7675F9CBF935}" uniqueName="11" name="Einddatum_werkelijk" queryTableFieldId="11" dataDxfId="19"/>
+    <tableColumn id="9" xr3:uid="{57E6EFC5-3E51-4CA8-999D-907B33F7A7EA}" uniqueName="9" name="Startdatum" queryTableFieldId="9" dataDxfId="19"/>
+    <tableColumn id="10" xr3:uid="{AAB42422-E2C6-40F3-98D1-D47D061F6522}" uniqueName="10" name="Einddatum_gepland" queryTableFieldId="10" dataDxfId="18"/>
+    <tableColumn id="11" xr3:uid="{F7A8C4D0-5031-4E2A-9F30-7675F9CBF935}" uniqueName="11" name="Einddatum_werkelijk" queryTableFieldId="11" dataDxfId="17"/>
     <tableColumn id="12" xr3:uid="{3739D346-F6CA-4A7E-91FC-8EEEC9F000FF}" uniqueName="12" name="Voortgang_pct" queryTableFieldId="12"/>
     <tableColumn id="13" xr3:uid="{F9E0DC93-D8FA-4078-A5A8-AF1A242311BF}" uniqueName="13" name="Budget_EUR" queryTableFieldId="13"/>
     <tableColumn id="14" xr3:uid="{D22E5635-4089-4D7D-9F21-4D47BB49B911}" uniqueName="14" name="Kosten_EUR" queryTableFieldId="14"/>
-    <tableColumn id="15" xr3:uid="{47082C6B-DA44-47B0-B6E5-7B3335F50164}" uniqueName="15" name="Risico" queryTableFieldId="15" dataDxfId="18"/>
-    <tableColumn id="16" xr3:uid="{D0960E6C-2C86-4E9F-9EDB-C96E40D07CB5}" uniqueName="16" name="Regio" queryTableFieldId="16" dataDxfId="17"/>
+    <tableColumn id="15" xr3:uid="{47082C6B-DA44-47B0-B6E5-7B3335F50164}" uniqueName="15" name="Risico" queryTableFieldId="15" dataDxfId="16"/>
+    <tableColumn id="16" xr3:uid="{D0960E6C-2C86-4E9F-9EDB-C96E40D07CB5}" uniqueName="16" name="Regio" queryTableFieldId="16" dataDxfId="15"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1192,22 +1198,22 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{DDAE2E8D-C7FF-490D-B63F-EED3D8F8F6F6}" name="Demo_XLS" displayName="Demo_XLS" ref="A1:P51" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:P51" xr:uid="{DDAE2E8D-C7FF-490D-B63F-EED3D8F8F6F6}"/>
   <tableColumns count="16">
-    <tableColumn id="17" xr3:uid="{0253E53A-40A2-4DC8-A9DD-E43E7FA56125}" uniqueName="17" name="Project_ID" queryTableFieldId="17" dataDxfId="16"/>
-    <tableColumn id="18" xr3:uid="{CC51713D-8C64-4013-8757-A5457F2FE0D9}" uniqueName="18" name="Projectnaam" queryTableFieldId="18" dataDxfId="15"/>
-    <tableColumn id="19" xr3:uid="{A1C2B82E-44B8-4820-A84A-0772B352AB67}" uniqueName="19" name="Categorie" queryTableFieldId="19" dataDxfId="14"/>
-    <tableColumn id="20" xr3:uid="{BDAC9E52-9FB5-415C-A09C-BB68FDEECBDC}" uniqueName="20" name="Afdeling" queryTableFieldId="20" dataDxfId="13"/>
-    <tableColumn id="21" xr3:uid="{695E3E88-9634-46FC-ACB8-11F49E458C94}" uniqueName="21" name="Projectleider" queryTableFieldId="21" dataDxfId="12"/>
-    <tableColumn id="22" xr3:uid="{40800C44-E907-4858-9480-1D613D69FD66}" uniqueName="22" name="Opdrachtgever" queryTableFieldId="22" dataDxfId="11"/>
-    <tableColumn id="23" xr3:uid="{860959CB-7913-4355-B863-A764DB83CDD0}" uniqueName="23" name="Prioriteit" queryTableFieldId="23" dataDxfId="10"/>
-    <tableColumn id="24" xr3:uid="{817E512B-CCEF-4AA4-A43E-727AE552BF37}" uniqueName="24" name="Status" queryTableFieldId="24" dataDxfId="9"/>
-    <tableColumn id="25" xr3:uid="{0E32CE31-BA04-40BC-AACF-A27111980187}" uniqueName="25" name="Startdatum" queryTableFieldId="25" dataDxfId="8"/>
-    <tableColumn id="26" xr3:uid="{51DFA4C1-1FBB-4B30-80AD-83EA699A08D2}" uniqueName="26" name="Einddatum_gepland" queryTableFieldId="26" dataDxfId="7"/>
+    <tableColumn id="17" xr3:uid="{0253E53A-40A2-4DC8-A9DD-E43E7FA56125}" uniqueName="17" name="Project_ID" queryTableFieldId="17" dataDxfId="14"/>
+    <tableColumn id="18" xr3:uid="{CC51713D-8C64-4013-8757-A5457F2FE0D9}" uniqueName="18" name="Projectnaam" queryTableFieldId="18" dataDxfId="13"/>
+    <tableColumn id="19" xr3:uid="{A1C2B82E-44B8-4820-A84A-0772B352AB67}" uniqueName="19" name="Categorie" queryTableFieldId="19" dataDxfId="12"/>
+    <tableColumn id="20" xr3:uid="{BDAC9E52-9FB5-415C-A09C-BB68FDEECBDC}" uniqueName="20" name="Afdeling" queryTableFieldId="20" dataDxfId="11"/>
+    <tableColumn id="21" xr3:uid="{695E3E88-9634-46FC-ACB8-11F49E458C94}" uniqueName="21" name="Projectleider" queryTableFieldId="21" dataDxfId="10"/>
+    <tableColumn id="22" xr3:uid="{40800C44-E907-4858-9480-1D613D69FD66}" uniqueName="22" name="Opdrachtgever" queryTableFieldId="22" dataDxfId="9"/>
+    <tableColumn id="23" xr3:uid="{860959CB-7913-4355-B863-A764DB83CDD0}" uniqueName="23" name="Prioriteit" queryTableFieldId="23" dataDxfId="8"/>
+    <tableColumn id="24" xr3:uid="{817E512B-CCEF-4AA4-A43E-727AE552BF37}" uniqueName="24" name="Status" queryTableFieldId="24" dataDxfId="7"/>
+    <tableColumn id="25" xr3:uid="{0E32CE31-BA04-40BC-AACF-A27111980187}" uniqueName="25" name="Startdatum" queryTableFieldId="25" dataDxfId="6"/>
+    <tableColumn id="26" xr3:uid="{51DFA4C1-1FBB-4B30-80AD-83EA699A08D2}" uniqueName="26" name="Einddatum_gepland" queryTableFieldId="26" dataDxfId="5"/>
     <tableColumn id="27" xr3:uid="{4071721A-8AC3-4759-9777-78D3DB85BF00}" uniqueName="27" name="Einddatum_werkelijk" queryTableFieldId="27"/>
-    <tableColumn id="28" xr3:uid="{A14EB393-22D2-41B5-AAAA-1644591BEBF8}" uniqueName="28" name="Voortgang_pct" queryTableFieldId="28" dataDxfId="6"/>
-    <tableColumn id="29" xr3:uid="{69240D3B-1B4C-43E3-BDDD-B7AC9C94B763}" uniqueName="29" name="Budget_EUR" queryTableFieldId="29" dataDxfId="5"/>
-    <tableColumn id="30" xr3:uid="{431A1335-744E-4332-B85D-1D12F08F2F11}" uniqueName="30" name="Kosten_EUR" queryTableFieldId="30" dataDxfId="4"/>
-    <tableColumn id="31" xr3:uid="{3AEF5743-4E87-4F42-B1FD-F6387F782FC4}" uniqueName="31" name="Risico" queryTableFieldId="31" dataDxfId="3"/>
-    <tableColumn id="32" xr3:uid="{C3CD2FB6-7D42-41F7-BDA8-54296D9F008B}" uniqueName="32" name="Regio" queryTableFieldId="32" dataDxfId="2"/>
+    <tableColumn id="28" xr3:uid="{A14EB393-22D2-41B5-AAAA-1644591BEBF8}" uniqueName="28" name="Voortgang_pct" queryTableFieldId="28" dataDxfId="4"/>
+    <tableColumn id="29" xr3:uid="{69240D3B-1B4C-43E3-BDDD-B7AC9C94B763}" uniqueName="29" name="Budget_EUR" queryTableFieldId="29" dataDxfId="3"/>
+    <tableColumn id="30" xr3:uid="{431A1335-744E-4332-B85D-1D12F08F2F11}" uniqueName="30" name="Kosten_EUR" queryTableFieldId="30" dataDxfId="2"/>
+    <tableColumn id="31" xr3:uid="{3AEF5743-4E87-4F42-B1FD-F6387F782FC4}" uniqueName="31" name="Risico" queryTableFieldId="31" dataDxfId="1"/>
+    <tableColumn id="32" xr3:uid="{C3CD2FB6-7D42-41F7-BDA8-54296D9F008B}" uniqueName="32" name="Regio" queryTableFieldId="32" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1538,7 +1544,7 @@
     <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="49.7109375" customWidth="1"/>
     <col min="5" max="5" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="28.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="23.140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="23.42578125" bestFit="1" customWidth="1"/>
@@ -1549,24 +1555,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A1" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
+      <c r="A1" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
       <c r="AA1" s="25" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" s="27" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AA2" s="25"/>
     </row>
@@ -1576,10 +1582,10 @@
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A4" s="28" t="s">
-        <v>44</v>
-      </c>
-      <c r="B4" s="28"/>
+      <c r="A4" s="29" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="29"/>
       <c r="AA4" s="22" t="str" cm="1">
         <f t="array" ref="AA4:AA5">_xlfn.UNIQUE(_xlfn._xlws.FILTER(cfg_paths[ID], cfg_paths[ID]&lt;&gt;""))</f>
         <v>path_dynamic</v>
@@ -1595,7 +1601,7 @@
         <v>27</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>4</v>
@@ -1641,7 +1647,7 @@
         <v>32</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C8" s="10"/>
       <c r="D8" s="10"/>
@@ -1753,10 +1759,10 @@
       <c r="J17" s="21"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="28" t="s">
-        <v>43</v>
-      </c>
-      <c r="B18" s="28"/>
+      <c r="A18" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="29"/>
       <c r="J18" s="21"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -1764,7 +1770,7 @@
         <v>27</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>3</v>
@@ -1776,19 +1782,19 @@
         <v>38</v>
       </c>
       <c r="F20" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H20" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="H20" s="3" t="s">
+      <c r="I20" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="I20" s="3" t="s">
+      <c r="J20" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="J20" s="4" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -1799,11 +1805,11 @@
         <v>33</v>
       </c>
       <c r="C21" s="7" t="str" cm="1">
-        <f t="array" aca="1" ref="C21" ca="1">IFERROR(IF(_xlfn.REGEXTEST(INDIRECT(cfg_sources[[#This Row],[Filepath]]), "://"), "src", ""),"")</f>
+        <f t="array" aca="1" ref="C21" ca="1">IFERROR(IF(_xlfn.REGEXTEST(INDIRECT(cfg_sources[[#This Row],[Filepath]]), "://"), "source_data", ""),"")</f>
         <v/>
       </c>
       <c r="D21" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>2</v>
@@ -1829,11 +1835,11 @@
         <v>33</v>
       </c>
       <c r="C22" s="7" t="str" cm="1">
-        <f t="array" aca="1" ref="C22" ca="1">IFERROR(IF(_xlfn.REGEXTEST(INDIRECT(cfg_sources[[#This Row],[Filepath]]), "://"), "src", ""),"")</f>
+        <f t="array" aca="1" ref="C22" ca="1">IFERROR(IF(_xlfn.REGEXTEST(INDIRECT(cfg_sources[[#This Row],[Filepath]]), "://"), "source_data", ""),"")</f>
         <v/>
       </c>
       <c r="D22" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E22" s="23" t="s">
         <v>12</v>
@@ -1841,14 +1847,14 @@
       <c r="F22" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="G22" s="23">
-        <v>27092026</v>
+      <c r="G22" s="28" t="s">
+        <v>54</v>
       </c>
       <c r="H22" s="23"/>
       <c r="I22" s="23"/>
       <c r="J22" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="J22" ca="1">IF(_xlfn.CONCAT(cfg_sources[[#This Row],[Filepath]:[REGEX replace with]])="","-",DATA.SOURCE($B22,$C22,$D22,$E22,$F22,$G22,$H22,$I22))</f>
-        <v>C:\Users\sgoos\Documents\demo_projects-27092026.xlsx</v>
+        <v>C:\Users\sgoos\Documents\demo_projects-27-09-2026.xlsx</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -1859,11 +1865,11 @@
         <v>33</v>
       </c>
       <c r="C23" s="7" t="str" cm="1">
-        <f t="array" aca="1" ref="C23" ca="1">IFERROR(IF(_xlfn.REGEXTEST(INDIRECT(cfg_sources[[#This Row],[Filepath]]), "://"), "src", ""),"")</f>
+        <f t="array" aca="1" ref="C23" ca="1">IFERROR(IF(_xlfn.REGEXTEST(INDIRECT(cfg_sources[[#This Row],[Filepath]]), "://"), "source_data", ""),"")</f>
         <v/>
       </c>
       <c r="D23" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E23" s="23" t="s">
         <v>30</v>
@@ -1872,7 +1878,7 @@
         <v>1</v>
       </c>
       <c r="G23" s="23" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H23" s="23"/>
       <c r="I23" s="23"/>
@@ -1885,7 +1891,7 @@
       <c r="A24" s="18"/>
       <c r="B24" s="7"/>
       <c r="C24" s="7" t="str" cm="1">
-        <f t="array" aca="1" ref="C24" ca="1">IFERROR(IF(_xlfn.REGEXTEST(INDIRECT(cfg_sources[[#This Row],[Filepath]]), "://"), "src", ""),"")</f>
+        <f t="array" aca="1" ref="C24" ca="1">IFERROR(IF(_xlfn.REGEXTEST(INDIRECT(cfg_sources[[#This Row],[Filepath]]), "://"), "source_data", ""),"")</f>
         <v/>
       </c>
       <c r="D24" s="23"/>
@@ -1903,7 +1909,7 @@
       <c r="A25" s="18"/>
       <c r="B25" s="7"/>
       <c r="C25" s="7" t="str" cm="1">
-        <f t="array" aca="1" ref="C25" ca="1">IFERROR(IF(_xlfn.REGEXTEST(INDIRECT(cfg_sources[[#This Row],[Filepath]]), "://"), "src", ""),"")</f>
+        <f t="array" aca="1" ref="C25" ca="1">IFERROR(IF(_xlfn.REGEXTEST(INDIRECT(cfg_sources[[#This Row],[Filepath]]), "://"), "source_data", ""),"")</f>
         <v/>
       </c>
       <c r="D25" s="23"/>
@@ -1921,7 +1927,7 @@
       <c r="A26" s="18"/>
       <c r="B26" s="7"/>
       <c r="C26" s="7" t="str" cm="1">
-        <f t="array" aca="1" ref="C26" ca="1">IFERROR(IF(_xlfn.REGEXTEST(INDIRECT(cfg_sources[[#This Row],[Filepath]]), "://"), "src", ""),"")</f>
+        <f t="array" aca="1" ref="C26" ca="1">IFERROR(IF(_xlfn.REGEXTEST(INDIRECT(cfg_sources[[#This Row],[Filepath]]), "://"), "source_data", ""),"")</f>
         <v/>
       </c>
       <c r="D26" s="23"/>
@@ -1939,7 +1945,7 @@
       <c r="A27" s="18"/>
       <c r="B27" s="7"/>
       <c r="C27" s="7" t="str" cm="1">
-        <f t="array" aca="1" ref="C27" ca="1">IFERROR(IF(_xlfn.REGEXTEST(INDIRECT(cfg_sources[[#This Row],[Filepath]]), "://"), "src", ""),"")</f>
+        <f t="array" aca="1" ref="C27" ca="1">IFERROR(IF(_xlfn.REGEXTEST(INDIRECT(cfg_sources[[#This Row],[Filepath]]), "://"), "source_data", ""),"")</f>
         <v/>
       </c>
       <c r="D27" s="23"/>
@@ -1957,7 +1963,7 @@
       <c r="A28" s="18"/>
       <c r="B28" s="7"/>
       <c r="C28" s="7" t="str" cm="1">
-        <f t="array" aca="1" ref="C28" ca="1">IFERROR(IF(_xlfn.REGEXTEST(INDIRECT(cfg_sources[[#This Row],[Filepath]]), "://"), "src", ""),"")</f>
+        <f t="array" aca="1" ref="C28" ca="1">IFERROR(IF(_xlfn.REGEXTEST(INDIRECT(cfg_sources[[#This Row],[Filepath]]), "://"), "source_data", ""),"")</f>
         <v/>
       </c>
       <c r="D28" s="23"/>
@@ -1975,7 +1981,7 @@
       <c r="A29" s="18"/>
       <c r="B29" s="7"/>
       <c r="C29" s="7" t="str" cm="1">
-        <f t="array" aca="1" ref="C29" ca="1">IFERROR(IF(_xlfn.REGEXTEST(INDIRECT(cfg_sources[[#This Row],[Filepath]]), "://"), "src", ""),"")</f>
+        <f t="array" aca="1" ref="C29" ca="1">IFERROR(IF(_xlfn.REGEXTEST(INDIRECT(cfg_sources[[#This Row],[Filepath]]), "://"), "source_data", ""),"")</f>
         <v/>
       </c>
       <c r="D29" s="23"/>
@@ -1993,7 +1999,7 @@
       <c r="A30" s="18"/>
       <c r="B30" s="7"/>
       <c r="C30" s="7" t="str" cm="1">
-        <f t="array" aca="1" ref="C30" ca="1">IFERROR(IF(_xlfn.REGEXTEST(INDIRECT(cfg_sources[[#This Row],[Filepath]]), "://"), "src", ""),"")</f>
+        <f t="array" aca="1" ref="C30" ca="1">IFERROR(IF(_xlfn.REGEXTEST(INDIRECT(cfg_sources[[#This Row],[Filepath]]), "://"), "source_data", ""),"")</f>
         <v/>
       </c>
       <c r="D30" s="23"/>
@@ -2011,7 +2017,7 @@
       <c r="A31" s="18"/>
       <c r="B31" s="7"/>
       <c r="C31" s="7" t="str" cm="1">
-        <f t="array" aca="1" ref="C31" ca="1">IFERROR(IF(_xlfn.REGEXTEST(INDIRECT(cfg_sources[[#This Row],[Filepath]]), "://"), "src", ""),"")</f>
+        <f t="array" aca="1" ref="C31" ca="1">IFERROR(IF(_xlfn.REGEXTEST(INDIRECT(cfg_sources[[#This Row],[Filepath]]), "://"), "source_data", ""),"")</f>
         <v/>
       </c>
       <c r="D31" s="23"/>
@@ -2029,7 +2035,7 @@
       <c r="A32" s="18"/>
       <c r="B32" s="7"/>
       <c r="C32" s="7" t="str" cm="1">
-        <f t="array" aca="1" ref="C32" ca="1">IFERROR(IF(_xlfn.REGEXTEST(INDIRECT(cfg_sources[[#This Row],[Filepath]]), "://"), "src", ""),"")</f>
+        <f t="array" aca="1" ref="C32" ca="1">IFERROR(IF(_xlfn.REGEXTEST(INDIRECT(cfg_sources[[#This Row],[Filepath]]), "://"), "source_data", ""),"")</f>
         <v/>
       </c>
       <c r="D32" s="23"/>
@@ -2047,7 +2053,7 @@
       <c r="A33" s="18"/>
       <c r="B33" s="7"/>
       <c r="C33" s="7" t="str" cm="1">
-        <f t="array" aca="1" ref="C33" ca="1">IFERROR(IF(_xlfn.REGEXTEST(INDIRECT(cfg_sources[[#This Row],[Filepath]]), "://"), "src", ""),"")</f>
+        <f t="array" aca="1" ref="C33" ca="1">IFERROR(IF(_xlfn.REGEXTEST(INDIRECT(cfg_sources[[#This Row],[Filepath]]), "://"), "source_data", ""),"")</f>
         <v/>
       </c>
       <c r="D33" s="23"/>
@@ -2065,7 +2071,7 @@
       <c r="A34" s="18"/>
       <c r="B34" s="7"/>
       <c r="C34" s="7" t="str" cm="1">
-        <f t="array" aca="1" ref="C34" ca="1">IFERROR(IF(_xlfn.REGEXTEST(INDIRECT(cfg_sources[[#This Row],[Filepath]]), "://"), "src", ""),"")</f>
+        <f t="array" aca="1" ref="C34" ca="1">IFERROR(IF(_xlfn.REGEXTEST(INDIRECT(cfg_sources[[#This Row],[Filepath]]), "://"), "source_data", ""),"")</f>
         <v/>
       </c>
       <c r="D34" s="23"/>
@@ -2083,7 +2089,7 @@
       <c r="A35" s="18"/>
       <c r="B35" s="7"/>
       <c r="C35" s="7" t="str" cm="1">
-        <f t="array" aca="1" ref="C35" ca="1">IFERROR(IF(_xlfn.REGEXTEST(INDIRECT(cfg_sources[[#This Row],[Filepath]]), "://"), "src", ""),"")</f>
+        <f t="array" aca="1" ref="C35" ca="1">IFERROR(IF(_xlfn.REGEXTEST(INDIRECT(cfg_sources[[#This Row],[Filepath]]), "://"), "source_data", ""),"")</f>
         <v/>
       </c>
       <c r="D35" s="23"/>
@@ -2101,7 +2107,7 @@
       <c r="A36" s="18"/>
       <c r="B36" s="7"/>
       <c r="C36" s="7" t="str" cm="1">
-        <f t="array" aca="1" ref="C36" ca="1">IFERROR(IF(_xlfn.REGEXTEST(INDIRECT(cfg_sources[[#This Row],[Filepath]]), "://"), "src", ""),"")</f>
+        <f t="array" aca="1" ref="C36" ca="1">IFERROR(IF(_xlfn.REGEXTEST(INDIRECT(cfg_sources[[#This Row],[Filepath]]), "://"), "source_data", ""),"")</f>
         <v/>
       </c>
       <c r="D36" s="23"/>
@@ -2119,7 +2125,7 @@
       <c r="A37" s="18"/>
       <c r="B37" s="7"/>
       <c r="C37" s="7" t="str" cm="1">
-        <f t="array" aca="1" ref="C37" ca="1">IFERROR(IF(_xlfn.REGEXTEST(INDIRECT(cfg_sources[[#This Row],[Filepath]]), "://"), "src", ""),"")</f>
+        <f t="array" aca="1" ref="C37" ca="1">IFERROR(IF(_xlfn.REGEXTEST(INDIRECT(cfg_sources[[#This Row],[Filepath]]), "://"), "source_data", ""),"")</f>
         <v/>
       </c>
       <c r="D37" s="23"/>
@@ -2137,7 +2143,7 @@
       <c r="A38" s="18"/>
       <c r="B38" s="7"/>
       <c r="C38" s="7" t="str" cm="1">
-        <f t="array" aca="1" ref="C38" ca="1">IFERROR(IF(_xlfn.REGEXTEST(INDIRECT(cfg_sources[[#This Row],[Filepath]]), "://"), "src", ""),"")</f>
+        <f t="array" aca="1" ref="C38" ca="1">IFERROR(IF(_xlfn.REGEXTEST(INDIRECT(cfg_sources[[#This Row],[Filepath]]), "://"), "source_data", ""),"")</f>
         <v/>
       </c>
       <c r="D38" s="23"/>
@@ -2155,7 +2161,7 @@
       <c r="A39" s="18"/>
       <c r="B39" s="7"/>
       <c r="C39" s="7" t="str" cm="1">
-        <f t="array" aca="1" ref="C39" ca="1">IFERROR(IF(_xlfn.REGEXTEST(INDIRECT(cfg_sources[[#This Row],[Filepath]]), "://"), "src", ""),"")</f>
+        <f t="array" aca="1" ref="C39" ca="1">IFERROR(IF(_xlfn.REGEXTEST(INDIRECT(cfg_sources[[#This Row],[Filepath]]), "://"), "source_data", ""),"")</f>
         <v/>
       </c>
       <c r="D39" s="23"/>
@@ -2173,7 +2179,7 @@
       <c r="A40" s="18"/>
       <c r="B40" s="7"/>
       <c r="C40" s="7" t="str" cm="1">
-        <f t="array" aca="1" ref="C40" ca="1">IFERROR(IF(_xlfn.REGEXTEST(INDIRECT(cfg_sources[[#This Row],[Filepath]]), "://"), "src", ""),"")</f>
+        <f t="array" aca="1" ref="C40" ca="1">IFERROR(IF(_xlfn.REGEXTEST(INDIRECT(cfg_sources[[#This Row],[Filepath]]), "://"), "source_data", ""),"")</f>
         <v/>
       </c>
       <c r="D40" s="23"/>
@@ -2191,7 +2197,7 @@
       <c r="A41" s="18"/>
       <c r="B41" s="7"/>
       <c r="C41" s="7" t="str" cm="1">
-        <f t="array" aca="1" ref="C41" ca="1">IFERROR(IF(_xlfn.REGEXTEST(INDIRECT(cfg_sources[[#This Row],[Filepath]]), "://"), "src", ""),"")</f>
+        <f t="array" aca="1" ref="C41" ca="1">IFERROR(IF(_xlfn.REGEXTEST(INDIRECT(cfg_sources[[#This Row],[Filepath]]), "://"), "source_data", ""),"")</f>
         <v/>
       </c>
       <c r="D41" s="23"/>
@@ -2209,7 +2215,7 @@
       <c r="A42" s="18"/>
       <c r="B42" s="7"/>
       <c r="C42" s="7" t="str" cm="1">
-        <f t="array" aca="1" ref="C42" ca="1">IFERROR(IF(_xlfn.REGEXTEST(INDIRECT(cfg_sources[[#This Row],[Filepath]]), "://"), "src", ""),"")</f>
+        <f t="array" aca="1" ref="C42" ca="1">IFERROR(IF(_xlfn.REGEXTEST(INDIRECT(cfg_sources[[#This Row],[Filepath]]), "://"), "source_data", ""),"")</f>
         <v/>
       </c>
       <c r="D42" s="23"/>
@@ -2227,7 +2233,7 @@
       <c r="A43" s="18"/>
       <c r="B43" s="7"/>
       <c r="C43" s="7" t="str" cm="1">
-        <f t="array" aca="1" ref="C43" ca="1">IFERROR(IF(_xlfn.REGEXTEST(INDIRECT(cfg_sources[[#This Row],[Filepath]]), "://"), "src", ""),"")</f>
+        <f t="array" aca="1" ref="C43" ca="1">IFERROR(IF(_xlfn.REGEXTEST(INDIRECT(cfg_sources[[#This Row],[Filepath]]), "://"), "source_data", ""),"")</f>
         <v/>
       </c>
       <c r="D43" s="23"/>
@@ -2245,7 +2251,7 @@
       <c r="A44" s="18"/>
       <c r="B44" s="7"/>
       <c r="C44" s="7" t="str" cm="1">
-        <f t="array" aca="1" ref="C44" ca="1">IFERROR(IF(_xlfn.REGEXTEST(INDIRECT(cfg_sources[[#This Row],[Filepath]]), "://"), "src", ""),"")</f>
+        <f t="array" aca="1" ref="C44" ca="1">IFERROR(IF(_xlfn.REGEXTEST(INDIRECT(cfg_sources[[#This Row],[Filepath]]), "://"), "source_data", ""),"")</f>
         <v/>
       </c>
       <c r="D44" s="23"/>
@@ -2263,7 +2269,7 @@
       <c r="A45" s="19"/>
       <c r="B45" s="7"/>
       <c r="C45" s="7" t="str" cm="1">
-        <f t="array" aca="1" ref="C45" ca="1">IFERROR(IF(_xlfn.REGEXTEST(INDIRECT(cfg_sources[[#This Row],[Filepath]]), "://"), "src", ""),"")</f>
+        <f t="array" aca="1" ref="C45" ca="1">IFERROR(IF(_xlfn.REGEXTEST(INDIRECT(cfg_sources[[#This Row],[Filepath]]), "://"), "source_data", ""),"")</f>
         <v/>
       </c>
       <c r="D45" s="20"/>
@@ -2278,10 +2284,10 @@
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A47" s="28" t="s">
-        <v>46</v>
-      </c>
-      <c r="B47" s="28"/>
+      <c r="A47" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="B47" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2382,7 +2388,7 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I2" s="26"/>
       <c r="J2" s="26"/>
@@ -2665,7 +2671,7 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -2763,7 +2769,7 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
